--- a/public/templates/upload_multiple_ticket.xlsx
+++ b/public/templates/upload_multiple_ticket.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CDA56E-8B3D-45F0-B4CC-CFBE3C31A4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{100E6049-D42B-4DF2-84AF-089950092CA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="New Sheet" sheetId="1" r:id="rId1"/>
@@ -15,10 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Parent Ticket</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Ticket Type</t>
   </si>
@@ -424,55 +421,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
         <v>7</v>
       </c>
       <c r="D1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
       </c>
       <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>9</v>
       </c>
       <c r="H1" t="s">
         <v>4</v>
       </c>
       <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
         <v>5</v>
-      </c>
-      <c r="J1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K1" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
